--- a/research/traditional_assets/database/data/malaysia/malaysia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0343</v>
+        <v>0.0312</v>
       </c>
       <c r="E2">
-        <v>0.397</v>
+        <v>-0.221</v>
       </c>
       <c r="G2">
-        <v>0.1003693592420106</v>
+        <v>0.07008718980549966</v>
       </c>
       <c r="H2">
-        <v>0.1003693592420106</v>
+        <v>0.07008718980549966</v>
       </c>
       <c r="I2">
-        <v>0.09442749317488355</v>
+        <v>0.03386988598256204</v>
       </c>
       <c r="J2">
-        <v>0.076491544750604</v>
+        <v>0.02592909931679391</v>
       </c>
       <c r="K2">
-        <v>43.5</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
-        <v>0.06985707403243938</v>
+        <v>0.01073105298457411</v>
       </c>
       <c r="M2">
-        <v>5.62</v>
+        <v>6.74</v>
       </c>
       <c r="N2">
-        <v>0.02669833729216152</v>
+        <v>0.04284806102987921</v>
       </c>
       <c r="O2">
-        <v>0.1291954022988506</v>
+        <v>1.053125</v>
       </c>
       <c r="P2">
-        <v>5.62</v>
+        <v>6.74</v>
       </c>
       <c r="Q2">
-        <v>0.02669833729216152</v>
+        <v>0.04284806102987921</v>
       </c>
       <c r="R2">
-        <v>0.1291954022988506</v>
+        <v>1.053125</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>22.5</v>
+        <v>25.5</v>
       </c>
       <c r="V2">
-        <v>0.1068883610451306</v>
+        <v>0.1621106166560712</v>
       </c>
       <c r="W2">
-        <v>0.07484514796971782</v>
+        <v>0.01069340016708438</v>
       </c>
       <c r="X2">
-        <v>0.1107070681156552</v>
+        <v>0.1564119339900749</v>
       </c>
       <c r="Y2">
-        <v>-0.03586192014593738</v>
+        <v>-0.1457185338229905</v>
       </c>
       <c r="Z2">
-        <v>0.9734250429889011</v>
+        <v>0.9129037195775295</v>
       </c>
       <c r="AA2">
-        <v>0.07445878523714415</v>
+        <v>0.02367077121159633</v>
       </c>
       <c r="AB2">
-        <v>0.08876454756847973</v>
+        <v>0.1221522743969673</v>
       </c>
       <c r="AC2">
-        <v>-0.01430576233133558</v>
+        <v>-0.09848150318537092</v>
       </c>
       <c r="AD2">
-        <v>77.3</v>
+        <v>71.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.3</v>
+        <v>71.8</v>
       </c>
       <c r="AG2">
-        <v>54.8</v>
+        <v>46.3</v>
       </c>
       <c r="AH2">
-        <v>0.268589298123697</v>
+        <v>0.3134002618943692</v>
       </c>
       <c r="AI2">
-        <v>0.1143829535365493</v>
+        <v>0.1201070592171295</v>
       </c>
       <c r="AJ2">
-        <v>0.2065586128910667</v>
+        <v>0.2274066797642436</v>
       </c>
       <c r="AK2">
-        <v>0.08388183070564825</v>
+        <v>0.08090162502184169</v>
       </c>
       <c r="AL2">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="AM2">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="AN2">
-        <v>1.290484140233723</v>
+        <v>3.094827586206896</v>
       </c>
       <c r="AO2">
-        <v>14.66334164588529</v>
+        <v>5.444743935309972</v>
       </c>
       <c r="AP2">
-        <v>0.9148580968280468</v>
+        <v>1.995689655172414</v>
       </c>
       <c r="AQ2">
-        <v>14.66334164588529</v>
+        <v>5.444743935309972</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0343</v>
+        <v>0.0312</v>
       </c>
       <c r="E3">
-        <v>0.397</v>
+        <v>-0.221</v>
       </c>
       <c r="G3">
-        <v>0.1003693592420106</v>
+        <v>0.07008718980549966</v>
       </c>
       <c r="H3">
-        <v>0.1003693592420106</v>
+        <v>0.07008718980549966</v>
       </c>
       <c r="I3">
-        <v>0.09442749317488355</v>
+        <v>0.03386988598256204</v>
       </c>
       <c r="J3">
-        <v>0.076491544750604</v>
+        <v>0.02592909931679391</v>
       </c>
       <c r="K3">
-        <v>43.5</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
-        <v>0.06985707403243938</v>
+        <v>0.01073105298457411</v>
       </c>
       <c r="M3">
-        <v>5.62</v>
+        <v>6.74</v>
       </c>
       <c r="N3">
-        <v>0.02669833729216152</v>
+        <v>0.04284806102987921</v>
       </c>
       <c r="O3">
-        <v>0.1291954022988506</v>
+        <v>1.053125</v>
       </c>
       <c r="P3">
-        <v>5.62</v>
+        <v>6.74</v>
       </c>
       <c r="Q3">
-        <v>0.02669833729216152</v>
+        <v>0.04284806102987921</v>
       </c>
       <c r="R3">
-        <v>0.1291954022988506</v>
+        <v>1.053125</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>22.5</v>
+        <v>25.5</v>
       </c>
       <c r="V3">
-        <v>0.1068883610451306</v>
+        <v>0.1621106166560712</v>
       </c>
       <c r="W3">
-        <v>0.07484514796971782</v>
+        <v>0.01069340016708438</v>
       </c>
       <c r="X3">
-        <v>0.1107070681156552</v>
+        <v>0.1564119339900749</v>
       </c>
       <c r="Y3">
-        <v>-0.03586192014593738</v>
+        <v>-0.1457185338229905</v>
       </c>
       <c r="Z3">
-        <v>0.9734250429889011</v>
+        <v>0.9129037195775295</v>
       </c>
       <c r="AA3">
-        <v>0.07445878523714415</v>
+        <v>0.02367077121159633</v>
       </c>
       <c r="AB3">
-        <v>0.08876454756847973</v>
+        <v>0.1221522743969673</v>
       </c>
       <c r="AC3">
-        <v>-0.01430576233133558</v>
+        <v>-0.09848150318537092</v>
       </c>
       <c r="AD3">
-        <v>77.3</v>
+        <v>71.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>77.3</v>
+        <v>71.8</v>
       </c>
       <c r="AG3">
-        <v>54.8</v>
+        <v>46.3</v>
       </c>
       <c r="AH3">
-        <v>0.268589298123697</v>
+        <v>0.3134002618943692</v>
       </c>
       <c r="AI3">
-        <v>0.1143829535365493</v>
+        <v>0.1201070592171295</v>
       </c>
       <c r="AJ3">
-        <v>0.2065586128910667</v>
+        <v>0.2274066797642436</v>
       </c>
       <c r="AK3">
-        <v>0.08388183070564825</v>
+        <v>0.08090162502184169</v>
       </c>
       <c r="AL3">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="AM3">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="AN3">
-        <v>1.290484140233723</v>
+        <v>3.094827586206896</v>
       </c>
       <c r="AO3">
-        <v>14.66334164588529</v>
+        <v>5.444743935309972</v>
       </c>
       <c r="AP3">
-        <v>0.9148580968280468</v>
+        <v>1.995689655172414</v>
       </c>
       <c r="AQ3">
-        <v>14.66334164588529</v>
+        <v>5.444743935309972</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_reinsurance.xlsx
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0312</v>
+        <v>0.112</v>
       </c>
       <c r="E2">
-        <v>-0.221</v>
+        <v>0.153</v>
+      </c>
+      <c r="F2">
+        <v>0.03</v>
       </c>
       <c r="G2">
-        <v>0.07008718980549966</v>
+        <v>0.06709781729991915</v>
       </c>
       <c r="H2">
-        <v>0.07008718980549966</v>
+        <v>0.06709781729991915</v>
       </c>
       <c r="I2">
-        <v>0.03386988598256204</v>
+        <v>0.09485313931554837</v>
       </c>
       <c r="J2">
-        <v>0.02592909931679391</v>
+        <v>0.07494569032339624</v>
       </c>
       <c r="K2">
-        <v>6.4</v>
+        <v>51.2</v>
       </c>
       <c r="L2">
-        <v>0.01073105298457411</v>
+        <v>0.06898410132039881</v>
       </c>
       <c r="M2">
-        <v>6.74</v>
+        <v>4.17</v>
       </c>
       <c r="N2">
-        <v>0.04284806102987921</v>
+        <v>0.0200192030724916</v>
       </c>
       <c r="O2">
-        <v>1.053125</v>
+        <v>0.08144531249999999</v>
       </c>
       <c r="P2">
-        <v>6.74</v>
+        <v>4.17</v>
       </c>
       <c r="Q2">
-        <v>0.04284806102987921</v>
+        <v>0.0200192030724916</v>
       </c>
       <c r="R2">
-        <v>1.053125</v>
+        <v>0.08144531249999999</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="V2">
-        <v>0.1621106166560712</v>
+        <v>0.2448391742678828</v>
       </c>
       <c r="W2">
-        <v>0.01069340016708438</v>
+        <v>0.0973384030418251</v>
       </c>
       <c r="X2">
-        <v>0.1564119339900749</v>
+        <v>0.1344323856780834</v>
       </c>
       <c r="Y2">
-        <v>-0.1457185338229905</v>
+        <v>-0.03709398263625825</v>
       </c>
       <c r="Z2">
-        <v>0.9129037195775295</v>
+        <v>1.296872269788573</v>
       </c>
       <c r="AA2">
-        <v>0.02367077121159633</v>
+        <v>0.09719498752057434</v>
       </c>
       <c r="AB2">
-        <v>0.1221522743969673</v>
+        <v>0.102994773427083</v>
       </c>
       <c r="AC2">
-        <v>-0.09848150318537092</v>
+        <v>-0.005799785906508634</v>
       </c>
       <c r="AD2">
-        <v>71.8</v>
+        <v>111.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>71.8</v>
+        <v>111.3</v>
       </c>
       <c r="AG2">
-        <v>46.3</v>
+        <v>60.3</v>
       </c>
       <c r="AH2">
-        <v>0.3134002618943692</v>
+        <v>0.3482478097622027</v>
       </c>
       <c r="AI2">
-        <v>0.1201070592171295</v>
+        <v>0.1611175448755067</v>
       </c>
       <c r="AJ2">
-        <v>0.2274066797642436</v>
+        <v>0.2244973938942665</v>
       </c>
       <c r="AK2">
-        <v>0.08090162502184169</v>
+        <v>0.09424820256330103</v>
       </c>
       <c r="AL2">
-        <v>3.71</v>
+        <v>5.66</v>
       </c>
       <c r="AM2">
-        <v>3.71</v>
+        <v>5.66</v>
       </c>
       <c r="AN2">
-        <v>3.094827586206896</v>
+        <v>1.543689320388349</v>
       </c>
       <c r="AO2">
-        <v>5.444743935309972</v>
+        <v>12.43816254416961</v>
       </c>
       <c r="AP2">
-        <v>1.995689655172414</v>
+        <v>0.8363384188626908</v>
       </c>
       <c r="AQ2">
-        <v>5.444743935309972</v>
+        <v>12.43816254416961</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0312</v>
+        <v>0.112</v>
       </c>
       <c r="E3">
-        <v>-0.221</v>
+        <v>0.153</v>
+      </c>
+      <c r="F3">
+        <v>0.03</v>
       </c>
       <c r="G3">
-        <v>0.07008718980549966</v>
+        <v>0.06709781729991915</v>
       </c>
       <c r="H3">
-        <v>0.07008718980549966</v>
+        <v>0.06709781729991915</v>
       </c>
       <c r="I3">
-        <v>0.03386988598256204</v>
+        <v>0.09485313931554837</v>
       </c>
       <c r="J3">
-        <v>0.02592909931679391</v>
+        <v>0.07494569032339624</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>51.2</v>
       </c>
       <c r="L3">
-        <v>0.01073105298457411</v>
+        <v>0.06898410132039881</v>
       </c>
       <c r="M3">
-        <v>6.74</v>
+        <v>4.17</v>
       </c>
       <c r="N3">
-        <v>0.04284806102987921</v>
+        <v>0.0200192030724916</v>
       </c>
       <c r="O3">
-        <v>1.053125</v>
+        <v>0.08144531249999999</v>
       </c>
       <c r="P3">
-        <v>6.74</v>
+        <v>4.17</v>
       </c>
       <c r="Q3">
-        <v>0.04284806102987921</v>
+        <v>0.0200192030724916</v>
       </c>
       <c r="R3">
-        <v>1.053125</v>
+        <v>0.08144531249999999</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="V3">
-        <v>0.1621106166560712</v>
+        <v>0.2448391742678828</v>
       </c>
       <c r="W3">
-        <v>0.01069340016708438</v>
+        <v>0.0973384030418251</v>
       </c>
       <c r="X3">
-        <v>0.1564119339900749</v>
+        <v>0.1344323856780834</v>
       </c>
       <c r="Y3">
-        <v>-0.1457185338229905</v>
+        <v>-0.03709398263625825</v>
       </c>
       <c r="Z3">
-        <v>0.9129037195775295</v>
+        <v>1.296872269788573</v>
       </c>
       <c r="AA3">
-        <v>0.02367077121159633</v>
+        <v>0.09719498752057434</v>
       </c>
       <c r="AB3">
-        <v>0.1221522743969673</v>
+        <v>0.102994773427083</v>
       </c>
       <c r="AC3">
-        <v>-0.09848150318537092</v>
+        <v>-0.005799785906508634</v>
       </c>
       <c r="AD3">
-        <v>71.8</v>
+        <v>111.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>71.8</v>
+        <v>111.3</v>
       </c>
       <c r="AG3">
-        <v>46.3</v>
+        <v>60.3</v>
       </c>
       <c r="AH3">
-        <v>0.3134002618943692</v>
+        <v>0.3482478097622027</v>
       </c>
       <c r="AI3">
-        <v>0.1201070592171295</v>
+        <v>0.1611175448755067</v>
       </c>
       <c r="AJ3">
-        <v>0.2274066797642436</v>
+        <v>0.2244973938942665</v>
       </c>
       <c r="AK3">
-        <v>0.08090162502184169</v>
+        <v>0.09424820256330103</v>
       </c>
       <c r="AL3">
-        <v>3.71</v>
+        <v>5.66</v>
       </c>
       <c r="AM3">
-        <v>3.71</v>
+        <v>5.66</v>
       </c>
       <c r="AN3">
-        <v>3.094827586206896</v>
+        <v>1.543689320388349</v>
       </c>
       <c r="AO3">
-        <v>5.444743935309972</v>
+        <v>12.43816254416961</v>
       </c>
       <c r="AP3">
-        <v>1.995689655172414</v>
+        <v>0.8363384188626908</v>
       </c>
       <c r="AQ3">
-        <v>5.444743935309972</v>
+        <v>12.43816254416961</v>
       </c>
     </row>
   </sheetData>
